--- a/untranslated/downloads/data-excel/3.5.1.1.xlsx
+++ b/untranslated/downloads/data-excel/3.5.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306FAD1D-1E51-4C88-890A-C4F1FFA01612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="43">
   <si>
     <t>3.5.1.1 Жынысы жана аймактар боюнча 100 000 калкка карата наркотиктен көз каранды болгондордун оорушу</t>
   </si>
@@ -148,11 +149,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +186,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="NTHarmonica"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -212,10 +233,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -258,9 +282,24 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Normal_PERVICHN" xfId="2" xr:uid="{98EDF7E1-7714-4D73-8D63-C006C6DBC385}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{596B52AD-6046-4BBF-A2EF-C5F2324B36A1}"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{773C90AB-310B-4FC9-9502-D587E430AAA0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -276,9 +315,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -316,9 +355,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -353,7 +392,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -388,7 +427,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -561,14 +600,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="42.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,7 +626,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -603,8 +642,9 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P2" s="16"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -650,8 +690,11 @@
       <c r="O3" s="5">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="17">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="13" customFormat="1">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -697,8 +740,11 @@
       <c r="O4" s="12">
         <v>2.3944505088207331</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="18">
+        <v>3.6278702407742709</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -744,8 +790,11 @@
       <c r="O5" s="7">
         <v>0.52951886522435021</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="23">
+        <v>0.13702849863903296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -791,8 +840,11 @@
       <c r="O6" s="7">
         <v>4.3000500913119915</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="23">
+        <v>7.1928512574335457</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="13" customFormat="1">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -838,8 +890,11 @@
       <c r="O7" s="12">
         <v>0.51981356020307379</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="18">
+        <v>1.0186117340676393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -885,8 +940,11 @@
       <c r="O8" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -932,8 +990,11 @@
       <c r="O9" s="7">
         <v>1.028739554007112</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="19">
+        <v>2.0142474435842859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="13" customFormat="1">
       <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
@@ -979,8 +1040,11 @@
       <c r="O10" s="12">
         <v>0.45336944169064486</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="18">
+        <v>2.5237754493062585</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
@@ -1026,8 +1090,11 @@
       <c r="O11" s="7">
         <v>0.15211161341746121</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -1073,8 +1140,11 @@
       <c r="O12" s="7">
         <v>0.75073722395392273</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="19">
+        <v>5.011733352201035</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="13" customFormat="1">
       <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
@@ -1120,8 +1190,11 @@
       <c r="O13" s="15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -1167,8 +1240,11 @@
       <c r="O14" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1214,8 +1290,11 @@
       <c r="O15" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="13" customFormat="1">
       <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
@@ -1261,8 +1340,11 @@
       <c r="O16" s="12">
         <v>0.32236434908190637</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="18">
+        <v>1.2760066097142384</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -1308,8 +1390,11 @@
       <c r="O17" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
@@ -1355,8 +1440,11 @@
       <c r="O18" s="7">
         <v>0.63756806039044667</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P18" s="19">
+        <v>2.5177184435464581</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="13" customFormat="1">
       <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1402,8 +1490,11 @@
       <c r="O19" s="12">
         <v>0.47449906455898705</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="18">
+        <v>0.21349638764112108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1449,8 +1540,11 @@
       <c r="O20" s="9">
         <v>0.13658701822343999</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="21">
+        <v>0.14384680890239129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
@@ -1496,8 +1590,11 @@
       <c r="O21" s="7">
         <v>0.80742182138214469</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="19">
+        <v>0.28169331485425186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="13" customFormat="1">
       <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
@@ -1543,8 +1640,11 @@
       <c r="O22" s="12">
         <v>1.4528231986808364</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="18">
+        <v>3.586749114072969</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
@@ -1590,8 +1690,11 @@
       <c r="O23" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -1637,8 +1740,11 @@
       <c r="O24" s="7">
         <v>2.8788783889796536</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="19">
+        <v>7.0966780450071321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="13" customFormat="1">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -1684,8 +1790,11 @@
       <c r="O25" s="12">
         <v>7.2371521991664292</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="18">
+        <v>14.205458628934757</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -1731,8 +1840,11 @@
       <c r="O26" s="7">
         <v>0.1843916182945988</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="21">
+        <v>0.20722468128844018</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="2" t="s">
         <v>38</v>
       </c>
@@ -1778,8 +1890,11 @@
       <c r="O27" s="7">
         <v>14.38048139128356</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="19">
+        <v>28.224551208882435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="13" customFormat="1">
       <c r="A28" s="6" t="s">
         <v>29</v>
       </c>
@@ -1825,8 +1940,11 @@
       <c r="O28" s="12">
         <v>5.7129502194292243</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="18">
+        <v>4.7388619546582627</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -1872,8 +1990,11 @@
       <c r="O29" s="7">
         <v>2.3720702955125175</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="21">
+        <v>0.42016335951417916</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="2" t="s">
         <v>38</v>
       </c>
@@ -1919,8 +2040,11 @@
       <c r="O30" s="7">
         <v>9.7530937387050578</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P30" s="19">
+        <v>9.9272617751626626</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="13" customFormat="1">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -1966,8 +2090,11 @@
       <c r="O31" s="12">
         <v>1.3736037318066185</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="18">
+        <v>1.2810849935838993</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -2013,8 +2140,11 @@
       <c r="O32" s="7">
         <v>0.56245500359971201</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P32" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" thickBot="1">
       <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
@@ -2059,6 +2189,9 @@
       </c>
       <c r="O33" s="10">
         <v>2.148066203400389</v>
+      </c>
+      <c r="P33" s="22">
+        <v>2.5311222574235708</v>
       </c>
     </row>
   </sheetData>
